--- a/output/pdf_financials_xlsx/INTR.xlsx
+++ b/output/pdf_financials_xlsx/INTR.xlsx
@@ -7714,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.424807</v>
+        <v>0.465854</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0.065</v>
@@ -38313,7 +38313,11 @@
           <t>Share-based compensation included in exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/INTR.xlsx
+++ b/output/pdf_financials_xlsx/INTR.xlsx
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.064706</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.043271</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000172</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0.000352</v>
@@ -1111,25 +1111,25 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>-0.000717</v>
+        <v>0.00565</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>-0.000115</v>
+        <v>0.031765</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.005998</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.052351</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.060154</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.164925</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.09802</v>
       </c>
     </row>
     <row r="13">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.511433</v>
+        <v>-0.576139</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.994135</v>
+        <v>-2.037406</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.498455</v>
+        <v>-0.498627</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.03885</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.37402</v>
+        <v>-1.380387</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-6.052205</v>
+        <v>-6.084085</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2124,13 +2124,13 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.025148</v>
+        <v>-2.077499</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.700586</v>
+        <v>-1.76074</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-5.880447</v>
+        <v>-6.045372</v>
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.511433</v>
+        <v>-0.576139</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.994135</v>
+        <v>-2.037406</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.498455</v>
+        <v>-0.498627</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.020698</v>
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.373039</v>
+        <v>-1.379406</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-6.049646</v>
+        <v>-6.081526</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.023409</v>
+        <v>-2.07576</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.700586</v>
+        <v>-1.76074</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-5.880447</v>
+        <v>-6.045372</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-12398.76286797905</v>
+        <v>-12456.25790139065</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-28858.68434861422</v>
+        <v>-29010.76181844202</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -2533,13 +2533,13 @@
         <v>0.140018</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.728442</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.36832</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.337865</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.163224</v>
@@ -2548,19 +2548,19 @@
         <v>0.7405620000000001</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.04564</v>
+        <v>0.239361</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.449109</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.884179</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.143106</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.295243</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>1.515878</v>
@@ -2653,13 +2653,13 @@
         <v>0.199518</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.733942</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.002842</v>
+        <v>0.371162</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.00114</v>
+        <v>0.339005</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.167204</v>
@@ -2668,19 +2668,19 @@
         <v>0.7486390000000001</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.050412</v>
+        <v>0.244133</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.1755</v>
+        <v>1.624609</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.884179</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.143106</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.295243</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>1.515878</v>
@@ -3373,13 +3373,13 @@
         <v>0.002033</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.733262</v>
+        <v>0.00482</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.37553</v>
+        <v>0.00721</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.344607</v>
+        <v>0.006742</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.006728</v>
@@ -3388,19 +3388,19 @@
         <v>0.188264</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.345936</v>
+        <v>0.152215</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.475182</v>
+        <v>0.026073</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.99703</v>
+        <v>0.112851</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.272826</v>
+        <v>0.12972</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.431586</v>
+        <v>0.136343</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0.29822</v>
@@ -10424,7 +10424,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -18305,7 +18305,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -18899,7 +18899,11 @@
           <t>RECLAMATION DEPOSITS (Note 6)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -19406,7 +19410,11 @@
           <t>RECLAMATION DEPOSITS</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -20408,7 +20416,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -34166,7 +34174,11 @@
           <t>Impairment of reclamation deposits</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -34568,7 +34580,11 @@
           <t>Reduction of reclamation deposits</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -36186,7 +36202,11 @@
           <t>Write-off of reclamation deposits</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -36800,7 +36820,11 @@
           <t>Recovery of reclamation deposits</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -44802,7 +44826,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -44905,7 +44929,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -45780,7 +45804,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -58869,7 +58893,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E502" s="5" t="n">
